--- a/interview_forms/041_performance_based_interview_question_evaluation_form--interview_forms.xlsx
+++ b/interview_forms/041_performance_based_interview_question_evaluation_form--interview_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -521,7 +521,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,18 +533,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>questions_1</t>
+          <t>favorite_books</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are your favorite books?</t>
+          <t>Favorite Books</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>questions_2</t>
+          <t>favorite_movies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What are your favorite movies?</t>
+          <t>Favorite Movies</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>questions_3</t>
+          <t>favorite_music</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What are your favorite movies?</t>
+          <t>Favorite Music</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>questions_4</t>
+          <t>favorite_sports_teams</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are your favorite music?</t>
+          <t>Favorite Sports Teams</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>questions_5</t>
+          <t>favorite_sport</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your favorite music?</t>
+          <t>Favorite Sport</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>questions_6</t>
+          <t>favorite_food</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What are your favorite sports teams?</t>
+          <t>Favorite Food</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>questions_7</t>
+          <t>favorite_color</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your favorite sport?</t>
+          <t>Favorite Color</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>questions_8</t>
+          <t>favorite_hobby</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your favorite food?</t>
+          <t>Favorite Hobby</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>questions_9</t>
+          <t>favorite_animal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Favorite Animal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,18 +740,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>questions_10</t>
+          <t>score1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Score 1-10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>questions_11</t>
+          <t>score2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Score 2-10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>questions_12</t>
+          <t>score3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Score 3-10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>questions_13</t>
+          <t>favorite_animal2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Favorite Animal2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>questions_14</t>
+          <t>favorite_animal3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Favorite Animal3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>questions_15</t>
+          <t>favorite_hobby2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your favorite color?</t>
+          <t>Favorite Hobby2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>favorite_hobby3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Score 1-10</t>
+          <t>Favorite Hobby3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>score_2</t>
+          <t>questions_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Score 1-10</t>
+          <t>What is your favorite hobby?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>score_3</t>
+          <t>questions_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Score 1-10</t>
+          <t>What is your favorite animal?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>questions_16</t>
+          <t>questions_18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is your favorite hobby?</t>
+          <t>Questions 18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,108 +970,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>questions_17</t>
+          <t>questions_19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is your favorite animal?</t>
+          <t>Questions 19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>questions_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is your favorite animal?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>questions_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is your favorite animal?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>questions_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your favorite animal?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>questions_21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is your favorite animal?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
